--- a/artfynd/A 45929-2023 artfynd.xlsx
+++ b/artfynd/A 45929-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137521066</v>
       </c>
       <c r="B2" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137521068</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137521061</v>
       </c>
       <c r="B4" t="n">
-        <v>80663</v>
+        <v>80666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137521062</v>
       </c>
       <c r="B5" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>137521063</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>137521064</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
